--- a/data.mn/public/datasets/mrpam-budget-revenue.xlsx
+++ b/data.mn/public/datasets/mrpam-budget-revenue.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y68"/>
+  <dimension ref="A1:Y70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5190,6 +5190,140 @@
         <v>293986.9</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="C69" t="n">
+        <v>29395.3</v>
+      </c>
+      <c r="D69" t="n">
+        <v>36605.2</v>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="I69" t="n">
+        <v>2926.2</v>
+      </c>
+      <c r="J69" t="n">
+        <v>3513.8</v>
+      </c>
+      <c r="K69" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="L69" t="n">
+        <v>143196.9</v>
+      </c>
+      <c r="M69" t="n">
+        <v>231472.9</v>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="R69" t="n">
+        <v>1596.4</v>
+      </c>
+      <c r="S69" t="n">
+        <v>2395</v>
+      </c>
+      <c r="T69" t="n">
+        <v>367.5</v>
+      </c>
+      <c r="U69" t="n">
+        <v>73508.2</v>
+      </c>
+      <c r="V69" t="n">
+        <v>20000</v>
+      </c>
+      <c r="W69" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="X69" t="n">
+        <v>250622.9</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>293986.9</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="C70" t="n">
+        <v>36456.6</v>
+      </c>
+      <c r="D70" t="n">
+        <v>36605.2</v>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="I70" t="n">
+        <v>3048.1</v>
+      </c>
+      <c r="J70" t="n">
+        <v>3513.8</v>
+      </c>
+      <c r="K70" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="L70" t="n">
+        <v>161176.3</v>
+      </c>
+      <c r="M70" t="n">
+        <v>231472.9</v>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="R70" t="n">
+        <v>1976.5</v>
+      </c>
+      <c r="S70" t="n">
+        <v>2395</v>
+      </c>
+      <c r="T70" t="n">
+        <v>838.6</v>
+      </c>
+      <c r="U70" t="n">
+        <v>167729.2</v>
+      </c>
+      <c r="V70" t="n">
+        <v>20000</v>
+      </c>
+      <c r="W70" t="n">
+        <v>126</v>
+      </c>
+      <c r="X70" t="n">
+        <v>370386.6</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>293986.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5201,7 +5335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y68"/>
+  <dimension ref="A1:Y70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -9977,6 +10111,140 @@
         <v>1456.5</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="C69" t="n">
+        <v>36605.2</v>
+      </c>
+      <c r="D69" t="n">
+        <v>29395.3</v>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="I69" t="n">
+        <v>3513.8</v>
+      </c>
+      <c r="J69" t="n">
+        <v>2926.2</v>
+      </c>
+      <c r="K69" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="L69" t="n">
+        <v>293986.9</v>
+      </c>
+      <c r="M69" t="n">
+        <v>250622.9</v>
+      </c>
+      <c r="N69" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="O69" t="n">
+        <v>231472.9</v>
+      </c>
+      <c r="P69" t="n">
+        <v>143196.9</v>
+      </c>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="n">
+        <v>367.5</v>
+      </c>
+      <c r="U69" t="n">
+        <v>20000</v>
+      </c>
+      <c r="V69" t="n">
+        <v>73508.2</v>
+      </c>
+      <c r="W69" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="X69" t="n">
+        <v>2395</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>1596.4</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="C70" t="n">
+        <v>36605.2</v>
+      </c>
+      <c r="D70" t="n">
+        <v>36456.6</v>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="I70" t="n">
+        <v>3513.8</v>
+      </c>
+      <c r="J70" t="n">
+        <v>3048.1</v>
+      </c>
+      <c r="K70" t="n">
+        <v>126</v>
+      </c>
+      <c r="L70" t="n">
+        <v>293986.9</v>
+      </c>
+      <c r="M70" t="n">
+        <v>370386.6</v>
+      </c>
+      <c r="N70" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="O70" t="n">
+        <v>231472.9</v>
+      </c>
+      <c r="P70" t="n">
+        <v>161176.3</v>
+      </c>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="n">
+        <v>838.6</v>
+      </c>
+      <c r="U70" t="n">
+        <v>20000</v>
+      </c>
+      <c r="V70" t="n">
+        <v>167729.2</v>
+      </c>
+      <c r="W70" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="X70" t="n">
+        <v>2395</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>1976.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
